--- a/integrity_system/app/static/discipline_template.xlsx
+++ b/integrity_system/app/static/discipline_template.xlsx
@@ -495,7 +495,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【违纪记录导入模板】*号为必填项。有无影响期填：有/无。状态填：completed/processing。日期格式：YYYY-MM-DD</t>
+          <t>【违纪记录导入模板】*号为必填项。有无影响期填：有/无。日期格式：YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -607,11 +607,7 @@
           <t>违反财务规定</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -660,11 +656,7 @@
           <t>业绩造假</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
